--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-del-maule.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-del-maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1469-2275-CM26</t>
+          <t>3756-429-CM24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>59382.8</v>
+        <v>313544.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4452-736-CM26</t>
+          <t>1469-573-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24725.55</v>
+        <v>21196.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1469-2464-CM26</t>
+          <t>872535-67-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FabricApp SpA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.650.494-9</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>40142.28</v>
+        <v>21737.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4168-1247-CM26</t>
+          <t>1469-796-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,616 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>13304.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2291-852-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SolNet SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45683.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1469-1704-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SOCIEDAD LIGARIUS SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.063.547-0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>41437.18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1469-2264-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>22060.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1469-2341-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SERVICIOS Y CONSULTORIAS EN INFORMATICA CLIOBYTE SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.479.175-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>24048.06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1233619-1034-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.980.930-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.046.871-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>13639.82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2298-5153-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.110.100-2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>51564.81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1469-2275-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>59382.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4452-736-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>INFO WORLD SA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.532.020-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>24725.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1469-2464-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FabricApp SpA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.650.494-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>40142.28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4168-1247-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>36252.2</v>
       </c>
     </row>
